--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/123.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/123.xlsx
@@ -426,13 +426,13 @@
         <v>-23.04357514145244</v>
       </c>
       <c r="E2">
-        <v>-18.41144183039596</v>
+        <v>-23.57002517383707</v>
       </c>
       <c r="F2">
-        <v>-0.7143601727671202</v>
+        <v>-2.059421743062817</v>
       </c>
       <c r="G2">
-        <v>-18.56510345153195</v>
+        <v>-18.03252069255091</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-23.17169303893332</v>
       </c>
       <c r="E3">
-        <v>-18.1300077713916</v>
+        <v>-23.67353565968578</v>
       </c>
       <c r="F3">
-        <v>-1.545870401492847</v>
+        <v>-2.022049119318115</v>
       </c>
       <c r="G3">
-        <v>-18.78201977662919</v>
+        <v>-18.03950835044903</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-23.04734331994853</v>
       </c>
       <c r="E4">
-        <v>-19.77877867560131</v>
+        <v>-24.06499659310749</v>
       </c>
       <c r="F4">
-        <v>-0.7305050534476826</v>
+        <v>-1.805099696524924</v>
       </c>
       <c r="G4">
-        <v>-17.83288880201914</v>
+        <v>-17.34599146263799</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.61662286681135</v>
       </c>
       <c r="E5">
-        <v>-20.34921394464386</v>
+        <v>-24.17682596123982</v>
       </c>
       <c r="F5">
-        <v>-0.5075201457576949</v>
+        <v>-2.013936088975097</v>
       </c>
       <c r="G5">
-        <v>-16.38595279712627</v>
+        <v>-17.0918093692472</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.89821379464029</v>
       </c>
       <c r="E6">
-        <v>-20.23813215455</v>
+        <v>-25.26847679191438</v>
       </c>
       <c r="F6">
-        <v>-0.0091353829655807</v>
+        <v>-1.67224613246394</v>
       </c>
       <c r="G6">
-        <v>-16.58676996570241</v>
+        <v>-17.28954455383353</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.92580462897911</v>
       </c>
       <c r="E7">
-        <v>-20.70447133494705</v>
+        <v>-26.11733504175079</v>
       </c>
       <c r="F7">
-        <v>-0.7488376524390384</v>
+        <v>-1.804921597533323</v>
       </c>
       <c r="G7">
-        <v>-16.63965451351229</v>
+        <v>-16.57238867912226</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.72236910155497</v>
       </c>
       <c r="E8">
-        <v>-21.43238807100445</v>
+        <v>-26.09568019790313</v>
       </c>
       <c r="F8">
-        <v>-0.2579620401533018</v>
+        <v>-1.538542663447683</v>
       </c>
       <c r="G8">
-        <v>-15.78405999074035</v>
+        <v>-16.0991546715587</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-18.347886547746</v>
       </c>
       <c r="E9">
-        <v>-21.6413070602773</v>
+        <v>-26.997541730667</v>
       </c>
       <c r="F9">
-        <v>-1.014554720969841</v>
+        <v>-1.468269771565992</v>
       </c>
       <c r="G9">
-        <v>-16.34297733041195</v>
+        <v>-15.70678978307717</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.86140422898241</v>
       </c>
       <c r="E10">
-        <v>-21.84563675103621</v>
+        <v>-27.11825066461181</v>
       </c>
       <c r="F10">
-        <v>-0.2367342970891617</v>
+        <v>-1.754491418418291</v>
       </c>
       <c r="G10">
-        <v>-15.04233962017129</v>
+        <v>-15.11873914451333</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.33535498428821</v>
       </c>
       <c r="E11">
-        <v>-23.51675608538482</v>
+        <v>-28.30416277951468</v>
       </c>
       <c r="F11">
-        <v>-0.1343074961004056</v>
+        <v>-1.645194138190716</v>
       </c>
       <c r="G11">
-        <v>-14.52102091872861</v>
+        <v>-14.83556734318282</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.86809329573376</v>
       </c>
       <c r="E12">
-        <v>-23.93460237035317</v>
+        <v>-28.58595609129864</v>
       </c>
       <c r="F12">
-        <v>-0.1476508382247</v>
+        <v>-1.507245286235112</v>
       </c>
       <c r="G12">
-        <v>-14.1282396164848</v>
+        <v>-14.02329421078352</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.51708345962834</v>
       </c>
       <c r="E13">
-        <v>-24.78824511963578</v>
+        <v>-29.30148172136841</v>
       </c>
       <c r="F13">
-        <v>-0.4250155808062669</v>
+        <v>-1.512069697989016</v>
       </c>
       <c r="G13">
-        <v>-14.35141389636693</v>
+        <v>-13.99055155749407</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.34390458020861</v>
       </c>
       <c r="E14">
-        <v>-24.96741880940021</v>
+        <v>-29.59456969135023</v>
       </c>
       <c r="F14">
-        <v>0.4320547525002416</v>
+        <v>-0.9882043538867892</v>
       </c>
       <c r="G14">
-        <v>-12.16880270000572</v>
+        <v>-13.14466639385648</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.37376730053148</v>
       </c>
       <c r="E15">
-        <v>-25.7329885593285</v>
+        <v>-30.86784460647087</v>
       </c>
       <c r="F15">
-        <v>0.1151246976587619</v>
+        <v>-0.935675920140467</v>
       </c>
       <c r="G15">
-        <v>-11.27740703665585</v>
+        <v>-12.85060648220873</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.601578926126464</v>
       </c>
       <c r="E16">
-        <v>-27.7872167191246</v>
+        <v>-30.91392240951418</v>
       </c>
       <c r="F16">
-        <v>0.6770990841267801</v>
+        <v>-0.778137007476057</v>
       </c>
       <c r="G16">
-        <v>-11.14961500503774</v>
+        <v>-12.36182157448821</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.026702407625001</v>
       </c>
       <c r="E17">
-        <v>-28.56593968931863</v>
+        <v>-31.42104820172671</v>
       </c>
       <c r="F17">
-        <v>-0.02039206760222318</v>
+        <v>-0.7064741150924689</v>
       </c>
       <c r="G17">
-        <v>-11.27741225814503</v>
+        <v>-12.45170951076024</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.612488157166966</v>
       </c>
       <c r="E18">
-        <v>-29.33643722448383</v>
+        <v>-32.14327919148042</v>
       </c>
       <c r="F18">
-        <v>1.08563911841126</v>
+        <v>-0.5450037707343725</v>
       </c>
       <c r="G18">
-        <v>-10.12004437883089</v>
+        <v>-11.78926048358345</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.325868391781915</v>
       </c>
       <c r="E19">
-        <v>-29.32645913427593</v>
+        <v>-33.00668198737637</v>
       </c>
       <c r="F19">
-        <v>0.2985219271689613</v>
+        <v>-0.5481051782904538</v>
       </c>
       <c r="G19">
-        <v>-10.04839902038927</v>
+        <v>-11.35025072686479</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.131421854498175</v>
       </c>
       <c r="E20">
-        <v>-29.35279464728666</v>
+        <v>-33.20771195173771</v>
       </c>
       <c r="F20">
-        <v>0.9162777461740954</v>
+        <v>-0.5092903668974774</v>
       </c>
       <c r="G20">
-        <v>-9.593170012898321</v>
+        <v>-11.14529291736715</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.979990994692563</v>
       </c>
       <c r="E21">
-        <v>-31.78846411818333</v>
+        <v>-33.87282382614105</v>
       </c>
       <c r="F21">
-        <v>0.523981996658514</v>
+        <v>-0.4367576887409499</v>
       </c>
       <c r="G21">
-        <v>-9.896204359078023</v>
+        <v>-11.25985891688668</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.848807247105116</v>
       </c>
       <c r="E22">
-        <v>-30.02204104356387</v>
+        <v>-34.58042512900305</v>
       </c>
       <c r="F22">
-        <v>0.5578266036346933</v>
+        <v>-0.1905064258085324</v>
       </c>
       <c r="G22">
-        <v>-8.568712529973173</v>
+        <v>-10.67562257617046</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.712691690984964</v>
       </c>
       <c r="E23">
-        <v>-31.43409343849799</v>
+        <v>-34.24877874508152</v>
       </c>
       <c r="F23">
-        <v>1.362719730973666</v>
+        <v>-0.005132711675253489</v>
       </c>
       <c r="G23">
-        <v>-9.426569262933313</v>
+        <v>-11.50039725904431</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.557963634041728</v>
       </c>
       <c r="E24">
-        <v>-32.84295201392332</v>
+        <v>-34.94200578354829</v>
       </c>
       <c r="F24">
-        <v>1.119295685987004</v>
+        <v>0.1421965727496526</v>
       </c>
       <c r="G24">
-        <v>-8.381823683790623</v>
+        <v>-10.61361217064234</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.393116865477666</v>
       </c>
       <c r="E25">
-        <v>-33.6899163993956</v>
+        <v>-35.30280563436445</v>
       </c>
       <c r="F25">
-        <v>-0.3036357336414581</v>
+        <v>-0.07824524701374065</v>
       </c>
       <c r="G25">
-        <v>-8.738097639044602</v>
+        <v>-10.80295903285742</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.22013047617198</v>
       </c>
       <c r="E26">
-        <v>-32.87058955868439</v>
+        <v>-35.67982169879841</v>
       </c>
       <c r="F26">
-        <v>0.3853265473083215</v>
+        <v>-0.2525627414218546</v>
       </c>
       <c r="G26">
-        <v>-9.756237120059257</v>
+        <v>-10.63220458824795</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.061668646574204</v>
       </c>
       <c r="E27">
-        <v>-32.51175625343053</v>
+        <v>-35.24300146789258</v>
       </c>
       <c r="F27">
-        <v>1.02689461567433</v>
+        <v>-0.1687518410762118</v>
       </c>
       <c r="G27">
-        <v>-8.567758302825121</v>
+        <v>-10.63131824045927</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.943021768914724</v>
       </c>
       <c r="E28">
-        <v>-32.87824392715605</v>
+        <v>-34.79501532833996</v>
       </c>
       <c r="F28">
-        <v>0.6674502606189715</v>
+        <v>-0.1623013441106121</v>
       </c>
       <c r="G28">
-        <v>-8.67997985370183</v>
+        <v>-10.62749219426099</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.883437272271904</v>
       </c>
       <c r="E29">
-        <v>-31.13988410145846</v>
+        <v>-34.71482720068583</v>
       </c>
       <c r="F29">
-        <v>0.4473265339382533</v>
+        <v>0.05242639730827016</v>
       </c>
       <c r="G29">
-        <v>-9.193736533436352</v>
+        <v>-11.02091704504651</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.913735716388988</v>
       </c>
       <c r="E30">
-        <v>-31.06341725115138</v>
+        <v>-34.43176508284214</v>
       </c>
       <c r="F30">
-        <v>1.061258609012065</v>
+        <v>-0.1681694987920438</v>
       </c>
       <c r="G30">
-        <v>-9.453958584438682</v>
+        <v>-10.66161462606684</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.045642603361165</v>
       </c>
       <c r="E31">
-        <v>-31.96272040573916</v>
+        <v>-34.31711983743157</v>
       </c>
       <c r="F31">
-        <v>-0.04317714138362638</v>
+        <v>0.05509705381489576</v>
       </c>
       <c r="G31">
-        <v>-9.289492118176911</v>
+        <v>-11.05974926009473</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.285561925354052</v>
       </c>
       <c r="E32">
-        <v>-30.63420362678698</v>
+        <v>-34.65549650030499</v>
       </c>
       <c r="F32">
-        <v>0.2844570770368285</v>
+        <v>-0.05947112819669266</v>
       </c>
       <c r="G32">
-        <v>-9.558030696074232</v>
+        <v>-10.76948406571017</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.636156969259931</v>
       </c>
       <c r="E33">
-        <v>-30.25573601499499</v>
+        <v>-34.37641523551615</v>
       </c>
       <c r="F33">
-        <v>0.5033631036354315</v>
+        <v>-0.1188004583199988</v>
       </c>
       <c r="G33">
-        <v>-9.888438699291756</v>
+        <v>-11.16400673459625</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.075839748301028</v>
       </c>
       <c r="E34">
-        <v>-29.52815984226623</v>
+        <v>-33.68528349216275</v>
       </c>
       <c r="F34">
-        <v>-0.2794150991510034</v>
+        <v>-0.1130706409948347</v>
       </c>
       <c r="G34">
-        <v>-9.693226799352738</v>
+        <v>-10.86438593696943</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.589557172057035</v>
       </c>
       <c r="E35">
-        <v>-31.11554212988364</v>
+        <v>-33.62095855516381</v>
       </c>
       <c r="F35">
-        <v>1.287472492838165</v>
+        <v>-0.08154794784870228</v>
       </c>
       <c r="G35">
-        <v>-9.126174379535229</v>
+        <v>-11.09879555619942</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.149795812343422</v>
       </c>
       <c r="E36">
-        <v>-30.82117289420811</v>
+        <v>-33.00056223048924</v>
       </c>
       <c r="F36">
-        <v>0.7553508108322354</v>
+        <v>-0.3198336298357997</v>
       </c>
       <c r="G36">
-        <v>-9.779417921283752</v>
+        <v>-11.29546033550339</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.72232286790107</v>
       </c>
       <c r="E37">
-        <v>-31.23059231339838</v>
+        <v>-32.98507698206461</v>
       </c>
       <c r="F37">
-        <v>1.064084998590417</v>
+        <v>-0.06866434963296157</v>
       </c>
       <c r="G37">
-        <v>-10.65708890031815</v>
+        <v>-11.14314949605785</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.29123984915442</v>
       </c>
       <c r="E38">
-        <v>-27.66463053366096</v>
+        <v>-32.39353509306928</v>
       </c>
       <c r="F38">
-        <v>0.9590331013021891</v>
+        <v>-0.2461453791523668</v>
       </c>
       <c r="G38">
-        <v>-9.806732836568274</v>
+        <v>-11.57409205198996</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.82716863945182</v>
       </c>
       <c r="E39">
-        <v>-28.48815004120459</v>
+        <v>-31.89631470986647</v>
       </c>
       <c r="F39">
-        <v>1.265477681559033</v>
+        <v>0.03855952698540643</v>
       </c>
       <c r="G39">
-        <v>-10.61240992275813</v>
+        <v>-11.38679723502349</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.31728517135016</v>
       </c>
       <c r="E40">
-        <v>-26.84496105301545</v>
+        <v>-31.40680061027688</v>
       </c>
       <c r="F40">
-        <v>1.338895884469153</v>
+        <v>-0.1173516437325025</v>
       </c>
       <c r="G40">
-        <v>-12.04784429235485</v>
+        <v>-11.71111437110995</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.75231991310468</v>
       </c>
       <c r="E41">
-        <v>-27.29342896508176</v>
+        <v>-31.333494353788</v>
       </c>
       <c r="F41">
-        <v>1.595476060547077</v>
+        <v>0.4208187770486691</v>
       </c>
       <c r="G41">
-        <v>-11.09408055146787</v>
+        <v>-11.60750697201162</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.11839141048698</v>
       </c>
       <c r="E42">
-        <v>-27.26197669571883</v>
+        <v>-30.26376832569721</v>
       </c>
       <c r="F42">
-        <v>1.055932206612064</v>
+        <v>0.1120489694921674</v>
       </c>
       <c r="G42">
-        <v>-11.70947090738984</v>
+        <v>-12.0361977607339</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.42402410160037</v>
       </c>
       <c r="E43">
-        <v>-26.91890067423137</v>
+        <v>-29.80890446819066</v>
       </c>
       <c r="F43">
-        <v>1.63914261981825</v>
+        <v>0.2761344697409018</v>
       </c>
       <c r="G43">
-        <v>-11.33043648079054</v>
+        <v>-11.52675664180849</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.66737307855699</v>
       </c>
       <c r="E44">
-        <v>-24.99169017638251</v>
+        <v>-30.2368015245651</v>
       </c>
       <c r="F44">
-        <v>1.591236476179549</v>
+        <v>0.1209605460114845</v>
       </c>
       <c r="G44">
-        <v>-11.70978289136848</v>
+        <v>-11.86504778831888</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.85631401514921</v>
       </c>
       <c r="E45">
-        <v>-26.59978037566552</v>
+        <v>-29.24822924576146</v>
       </c>
       <c r="F45">
-        <v>2.112630800319225</v>
+        <v>0.1163647636607528</v>
       </c>
       <c r="G45">
-        <v>-11.55699689640735</v>
+        <v>-11.97110406584367</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.0076450865249</v>
       </c>
       <c r="E46">
-        <v>-25.68026769477113</v>
+        <v>-28.63761581036252</v>
       </c>
       <c r="F46">
-        <v>1.597979386838337</v>
+        <v>0.2537039372078969</v>
       </c>
       <c r="G46">
-        <v>-12.80382454988057</v>
+        <v>-12.10167262433443</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.12392833955978</v>
       </c>
       <c r="E47">
-        <v>-25.28182521311238</v>
+        <v>-28.35960399748982</v>
       </c>
       <c r="F47">
-        <v>1.613380393591186</v>
+        <v>0.6620683576029831</v>
       </c>
       <c r="G47">
-        <v>-12.63915575091299</v>
+        <v>-12.64592019014856</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.22649420957821</v>
       </c>
       <c r="E48">
-        <v>-24.0654492931419</v>
+        <v>-28.1062124213507</v>
       </c>
       <c r="F48">
-        <v>1.222523518254267</v>
+        <v>0.4657220888522219</v>
       </c>
       <c r="G48">
-        <v>-13.17672503206306</v>
+        <v>-12.39816313919651</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-13.32511654179683</v>
       </c>
       <c r="E49">
-        <v>-24.92561673741581</v>
+        <v>-27.87793946730415</v>
       </c>
       <c r="F49">
-        <v>2.496141713528118</v>
+        <v>0.4424515917727782</v>
       </c>
       <c r="G49">
-        <v>-11.96188422132015</v>
+        <v>-12.82789953112752</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-13.4236209255649</v>
       </c>
       <c r="E50">
-        <v>-24.40706753745434</v>
+        <v>-27.41188685848852</v>
       </c>
       <c r="F50">
-        <v>2.100526695829519</v>
+        <v>0.2452131713292019</v>
       </c>
       <c r="G50">
-        <v>-11.73734321664457</v>
+        <v>-12.98017512552109</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-13.53920468327945</v>
       </c>
       <c r="E51">
-        <v>-23.41920545778725</v>
+        <v>-27.21506617380489</v>
       </c>
       <c r="F51">
-        <v>1.814141860598868</v>
+        <v>0.3162812959175799</v>
       </c>
       <c r="G51">
-        <v>-12.68346139199648</v>
+        <v>-12.53208780985914</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.66292613568694</v>
       </c>
       <c r="E52">
-        <v>-22.4110258683191</v>
+        <v>-26.66003516556613</v>
       </c>
       <c r="F52">
-        <v>1.448778820450507</v>
+        <v>0.3692090027520515</v>
       </c>
       <c r="G52">
-        <v>-13.17692867014116</v>
+        <v>-13.01713543669748</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.80140455522074</v>
       </c>
       <c r="E53">
-        <v>-21.42325515930115</v>
+        <v>-25.5561448211173</v>
       </c>
       <c r="F53">
-        <v>1.607331654815944</v>
+        <v>0.5068770381581069</v>
       </c>
       <c r="G53">
-        <v>-13.82471967181115</v>
+        <v>-13.23411050354802</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.95222682081436</v>
       </c>
       <c r="E54">
-        <v>-21.16335550101603</v>
+        <v>-26.16930002184704</v>
       </c>
       <c r="F54">
-        <v>1.823139587328076</v>
+        <v>0.2229010953347972</v>
       </c>
       <c r="G54">
-        <v>-14.28358283577292</v>
+        <v>-12.83069041709543</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.10183741692291</v>
       </c>
       <c r="E55">
-        <v>-21.07914083498248</v>
+        <v>-25.06727862249438</v>
       </c>
       <c r="F55">
-        <v>1.270727874157976</v>
+        <v>0.1546817262446467</v>
       </c>
       <c r="G55">
-        <v>-13.20014602178994</v>
+        <v>-13.45749364299745</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.25683490496453</v>
       </c>
       <c r="E56">
-        <v>-21.5304038582704</v>
+        <v>-25.704584747078</v>
       </c>
       <c r="F56">
-        <v>1.39779943374742</v>
+        <v>0.06261945819971808</v>
       </c>
       <c r="G56">
-        <v>-12.79998153384246</v>
+        <v>-13.57273190924919</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.40037708452784</v>
       </c>
       <c r="E57">
-        <v>-22.00236233358994</v>
+        <v>-24.10068098481042</v>
       </c>
       <c r="F57">
-        <v>1.21112352605694</v>
+        <v>0.2118158827505342</v>
       </c>
       <c r="G57">
-        <v>-13.347693557729</v>
+        <v>-14.02293523340224</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-14.53036377214274</v>
       </c>
       <c r="E58">
-        <v>-21.05171718060464</v>
+        <v>-24.41879620623566</v>
       </c>
       <c r="F58">
-        <v>1.166076906692703</v>
+        <v>0.1757570497066717</v>
       </c>
       <c r="G58">
-        <v>-14.03723689227236</v>
+        <v>-13.59115593382868</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-14.64562253145655</v>
       </c>
       <c r="E59">
-        <v>-19.2855640647213</v>
+        <v>-24.43495219828924</v>
       </c>
       <c r="F59">
-        <v>1.900098232517762</v>
+        <v>0.340967472888408</v>
       </c>
       <c r="G59">
-        <v>-15.10603526133298</v>
+        <v>-13.91600305106713</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-14.73093457727784</v>
       </c>
       <c r="E60">
-        <v>-20.51691646472911</v>
+        <v>-23.85781364616842</v>
       </c>
       <c r="F60">
-        <v>1.788629801327449</v>
+        <v>0.2972768909625536</v>
       </c>
       <c r="G60">
-        <v>-14.81097412913454</v>
+        <v>-13.92881789089261</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-14.79269346132281</v>
       </c>
       <c r="E61">
-        <v>-19.75650915647758</v>
+        <v>-24.10189787572859</v>
       </c>
       <c r="F61">
-        <v>0.92610881051052</v>
+        <v>0.1120572531661954</v>
       </c>
       <c r="G61">
-        <v>-14.66064484483364</v>
+        <v>-13.77122159902235</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-14.82117741734604</v>
       </c>
       <c r="E62">
-        <v>-19.65871764262317</v>
+        <v>-23.49663377651603</v>
       </c>
       <c r="F62">
-        <v>1.723541661019881</v>
+        <v>0.128147461598173</v>
       </c>
       <c r="G62">
-        <v>-13.49404667801763</v>
+        <v>-13.97746520023112</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-14.81060624164913</v>
       </c>
       <c r="E63">
-        <v>-19.90397723098827</v>
+        <v>-23.15688032408843</v>
       </c>
       <c r="F63">
-        <v>1.231531185392309</v>
+        <v>0.05694762659274986</v>
       </c>
       <c r="G63">
-        <v>-14.25007131820139</v>
+        <v>-14.51357376978246</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-14.76911711700016</v>
       </c>
       <c r="E64">
-        <v>-17.63204188675599</v>
+        <v>-23.27469862295116</v>
       </c>
       <c r="F64">
-        <v>1.430221733892993</v>
+        <v>-0.2255670761320215</v>
       </c>
       <c r="G64">
-        <v>-14.59849084835301</v>
+        <v>-14.10291931006788</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.68624044386147</v>
       </c>
       <c r="E65">
-        <v>-16.93343020980658</v>
+        <v>-22.85864652527514</v>
       </c>
       <c r="F65">
-        <v>1.618580884145961</v>
+        <v>-0.07067893915656998</v>
       </c>
       <c r="G65">
-        <v>-14.93312825780814</v>
+        <v>-14.28940479621111</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.57480761837998</v>
       </c>
       <c r="E66">
-        <v>-19.19036000152225</v>
+        <v>-22.42968624680155</v>
       </c>
       <c r="F66">
-        <v>0.9141007966395382</v>
+        <v>-0.2063125042213498</v>
       </c>
       <c r="G66">
-        <v>-14.39414525846198</v>
+        <v>-14.29303112044816</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.43971241197687</v>
       </c>
       <c r="E67">
-        <v>-18.89239200823376</v>
+        <v>-22.57398126786007</v>
       </c>
       <c r="F67">
-        <v>0.9755673146620673</v>
+        <v>-0.1582779636352149</v>
       </c>
       <c r="G67">
-        <v>-15.6603929355762</v>
+        <v>-14.50383047096842</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.28169343067571</v>
       </c>
       <c r="E68">
-        <v>-16.80120442085801</v>
+        <v>-22.58607957244929</v>
       </c>
       <c r="F68">
-        <v>0.7716017225403562</v>
+        <v>-0.2244835715691598</v>
       </c>
       <c r="G68">
-        <v>-14.62612296910535</v>
+        <v>-14.10760298586434</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.12098761634992</v>
       </c>
       <c r="E69">
-        <v>-17.00688805850882</v>
+        <v>-22.56795495822774</v>
       </c>
       <c r="F69">
-        <v>1.30471578869484</v>
+        <v>-0.2425229284999246</v>
       </c>
       <c r="G69">
-        <v>-14.58447245527103</v>
+        <v>-14.29146728443809</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-13.95281850935182</v>
       </c>
       <c r="E70">
-        <v>-18.45573998238658</v>
+        <v>-22.89625385382146</v>
       </c>
       <c r="F70">
-        <v>0.8626790617433562</v>
+        <v>-0.07078248508191991</v>
       </c>
       <c r="G70">
-        <v>-13.68101906802709</v>
+        <v>-14.32413683687898</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-13.78946202779961</v>
       </c>
       <c r="E71">
-        <v>-17.64336354082747</v>
+        <v>-23.19410555719287</v>
       </c>
       <c r="F71">
-        <v>0.757501252609903</v>
+        <v>-0.09419960319165913</v>
       </c>
       <c r="G71">
-        <v>-14.40643011713546</v>
+        <v>-13.82160505351395</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-13.63715067038879</v>
       </c>
       <c r="E72">
-        <v>-17.84094010997221</v>
+        <v>-22.65973677529513</v>
       </c>
       <c r="F72">
-        <v>1.249074350248797</v>
+        <v>-0.3932510043785171</v>
       </c>
       <c r="G72">
-        <v>-14.37743127158967</v>
+        <v>-14.11561405564217</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-13.48891616454328</v>
       </c>
       <c r="E73">
-        <v>-17.52290379956214</v>
+        <v>-23.19538474628092</v>
       </c>
       <c r="F73">
-        <v>0.8848627407903269</v>
+        <v>-0.2774402712627294</v>
       </c>
       <c r="G73">
-        <v>-14.36163104532426</v>
+        <v>-13.56049926546753</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.35786895585311</v>
       </c>
       <c r="E74">
-        <v>-17.94568409958439</v>
+        <v>-23.46802645691061</v>
       </c>
       <c r="F74">
-        <v>1.008726861796131</v>
+        <v>-0.6180955968877897</v>
       </c>
       <c r="G74">
-        <v>-13.65734483607488</v>
+        <v>-14.08562051640717</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.23752081953657</v>
       </c>
       <c r="E75">
-        <v>-20.56978269168286</v>
+        <v>-23.38194699899221</v>
       </c>
       <c r="F75">
-        <v>1.143701046408283</v>
+        <v>-0.3159038548769188</v>
       </c>
       <c r="G75">
-        <v>-13.54165882712576</v>
+        <v>-13.9433610436374</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.12898935940201</v>
       </c>
       <c r="E76">
-        <v>-18.21918967816965</v>
+        <v>-23.56614192124836</v>
       </c>
       <c r="F76">
-        <v>0.4573481227773217</v>
+        <v>-0.3619213208372369</v>
       </c>
       <c r="G76">
-        <v>-14.51095258221298</v>
+        <v>-13.3292147075131</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.04034851387175</v>
       </c>
       <c r="E77">
-        <v>-18.59204007164481</v>
+        <v>-23.59577093083968</v>
       </c>
       <c r="F77">
-        <v>1.217578164859554</v>
+        <v>-0.7037214502129662</v>
       </c>
       <c r="G77">
-        <v>-13.4631772339723</v>
+        <v>-13.74862038309708</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-12.95996963066502</v>
       </c>
       <c r="E78">
-        <v>-21.32857440072903</v>
+        <v>-24.64081857723834</v>
       </c>
       <c r="F78">
-        <v>1.143826958253508</v>
+        <v>-0.5342540469482433</v>
       </c>
       <c r="G78">
-        <v>-14.72587168769802</v>
+        <v>-13.41454428372904</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.89559206014738</v>
       </c>
       <c r="E79">
-        <v>-19.88462326621457</v>
+        <v>-24.27311816580597</v>
       </c>
       <c r="F79">
-        <v>0.5053337896866914</v>
+        <v>-0.7442385566186955</v>
       </c>
       <c r="G79">
-        <v>-13.04477277893901</v>
+        <v>-12.84701801376825</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.84162382272843</v>
       </c>
       <c r="E80">
-        <v>-20.89993807273878</v>
+        <v>-25.22491791153958</v>
       </c>
       <c r="F80">
-        <v>1.02800131452447</v>
+        <v>-0.6467372282069853</v>
       </c>
       <c r="G80">
-        <v>-13.31315210141627</v>
+        <v>-12.83183261785404</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.78930996852747</v>
       </c>
       <c r="E81">
-        <v>-22.34581214409664</v>
+        <v>-25.64121920189509</v>
       </c>
       <c r="F81">
-        <v>1.390763281028041</v>
+        <v>-0.818213422423497</v>
       </c>
       <c r="G81">
-        <v>-11.76516983786895</v>
+        <v>-12.4406451751831</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.74726144723007</v>
       </c>
       <c r="E82">
-        <v>-21.89183292060228</v>
+        <v>-26.32071780032764</v>
       </c>
       <c r="F82">
-        <v>1.223505961993987</v>
+        <v>-0.7940300644661683</v>
       </c>
       <c r="G82">
-        <v>-13.35361211571705</v>
+        <v>-12.67620352203318</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.70200456575921</v>
       </c>
       <c r="E83">
-        <v>-21.75128409615876</v>
+        <v>-27.07241582443101</v>
       </c>
       <c r="F83">
-        <v>0.5325067256007237</v>
+        <v>-0.9432670790197216</v>
       </c>
       <c r="G83">
-        <v>-13.08815030032036</v>
+        <v>-12.44920319595277</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.65881982514685</v>
       </c>
       <c r="E84">
-        <v>-23.05046259031235</v>
+        <v>-27.19524289615149</v>
       </c>
       <c r="F84">
-        <v>1.326687405686694</v>
+        <v>-0.8925270904960435</v>
       </c>
       <c r="G84">
-        <v>-12.63420577916824</v>
+        <v>-12.39928967548757</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.61791637353639</v>
       </c>
       <c r="E85">
-        <v>-24.77174856425356</v>
+        <v>-27.83200079684022</v>
       </c>
       <c r="F85">
-        <v>1.157581170609591</v>
+        <v>-0.7513252397496454</v>
       </c>
       <c r="G85">
-        <v>-13.46749410015371</v>
+        <v>-11.93344668586145</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.57074165726605</v>
       </c>
       <c r="E86">
-        <v>-25.56789425595525</v>
+        <v>-29.16878454293447</v>
       </c>
       <c r="F86">
-        <v>0.8531395827327171</v>
+        <v>-0.7849751803861669</v>
       </c>
       <c r="G86">
-        <v>-11.81971351386649</v>
+        <v>-12.04083313775542</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.52989368025656</v>
       </c>
       <c r="E87">
-        <v>-24.52079907637345</v>
+        <v>-29.8612515437288</v>
       </c>
       <c r="F87">
-        <v>0.2441644581972577</v>
+        <v>-0.7449219597260052</v>
       </c>
       <c r="G87">
-        <v>-11.62279157622029</v>
+        <v>-11.80852386254898</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.49015608951209</v>
       </c>
       <c r="E88">
-        <v>-28.64538646875127</v>
+        <v>-30.62718469964802</v>
       </c>
       <c r="F88">
-        <v>1.238081914813647</v>
+        <v>-0.7770659284242372</v>
       </c>
       <c r="G88">
-        <v>-11.59808610015459</v>
+        <v>-11.79834065327134</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-12.45788189686751</v>
       </c>
       <c r="E89">
-        <v>-28.33694407650155</v>
+        <v>-31.84163145295812</v>
       </c>
       <c r="F89">
-        <v>1.715039297997547</v>
+        <v>-0.7291929194816481</v>
       </c>
       <c r="G89">
-        <v>-11.18080557066777</v>
+        <v>-11.14413635751329</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-12.44564049658282</v>
       </c>
       <c r="E90">
-        <v>-30.0446199769313</v>
+        <v>-32.92853308648274</v>
       </c>
       <c r="F90">
-        <v>0.8214942912109704</v>
+        <v>-1.00615673224026</v>
       </c>
       <c r="G90">
-        <v>-11.36611883248958</v>
+        <v>-11.71346665198654</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-12.44924156226883</v>
       </c>
       <c r="E91">
-        <v>-31.79691382662369</v>
+        <v>-33.72709802378113</v>
       </c>
       <c r="F91">
-        <v>1.084928379179658</v>
+        <v>-1.033384340402877</v>
       </c>
       <c r="G91">
-        <v>-11.12248545261918</v>
+        <v>-11.36126154217781</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.4821780419225</v>
       </c>
       <c r="E92">
-        <v>-33.95308878820469</v>
+        <v>-35.76961205103554</v>
       </c>
       <c r="F92">
-        <v>0.3475505086384556</v>
+        <v>-1.179492611276057</v>
       </c>
       <c r="G92">
-        <v>-11.60180380045233</v>
+        <v>-11.12293058457197</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.54213628186505</v>
       </c>
       <c r="E93">
-        <v>-34.36757927842257</v>
+        <v>-36.80692641794737</v>
       </c>
       <c r="F93">
-        <v>0.7185779250871598</v>
+        <v>-1.01036732374869</v>
       </c>
       <c r="G93">
-        <v>-11.00312873677496</v>
+        <v>-11.27026926094374</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.62080681634263</v>
       </c>
       <c r="E94">
-        <v>-36.48909569149788</v>
+        <v>-38.92806488879211</v>
       </c>
       <c r="F94">
-        <v>1.158986081724739</v>
+        <v>-1.204612024398549</v>
       </c>
       <c r="G94">
-        <v>-11.14658131982286</v>
+        <v>-11.40776673557932</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.72132098053946</v>
       </c>
       <c r="E95">
-        <v>-37.3945455988464</v>
+        <v>-40.35897286314096</v>
       </c>
       <c r="F95">
-        <v>0.7242820630228372</v>
+        <v>-1.797445581723057</v>
       </c>
       <c r="G95">
-        <v>-11.96390754837827</v>
+        <v>-11.51137282930535</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.81815820586699</v>
       </c>
       <c r="E96">
-        <v>-40.80078940727056</v>
+        <v>-41.95014080288096</v>
       </c>
       <c r="F96">
-        <v>0.3123291550388235</v>
+        <v>-1.533673519854027</v>
       </c>
       <c r="G96">
-        <v>-10.72592640295203</v>
+        <v>-11.46342389414496</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.90369980797033</v>
       </c>
       <c r="E97">
-        <v>-42.27310074531661</v>
+        <v>-43.07515438012786</v>
       </c>
       <c r="F97">
-        <v>-0.06188416244104762</v>
+        <v>-1.493354393257567</v>
       </c>
       <c r="G97">
-        <v>-12.05803794461086</v>
+        <v>-11.5249004024042</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.95670369561686</v>
       </c>
       <c r="E98">
-        <v>-45.24567868683614</v>
+        <v>-45.61509852775699</v>
       </c>
       <c r="F98">
-        <v>-0.3041087314284567</v>
+        <v>-1.673993159316444</v>
       </c>
       <c r="G98">
-        <v>-11.58476738662302</v>
+        <v>-11.90360718055732</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.95876826632982</v>
       </c>
       <c r="E99">
-        <v>-45.62652297380876</v>
+        <v>-47.21275066867788</v>
       </c>
       <c r="F99">
-        <v>-0.3465575906175145</v>
+        <v>-2.016494915882344</v>
       </c>
       <c r="G99">
-        <v>-12.02986409435586</v>
+        <v>-11.88332691657356</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.89893738331836</v>
       </c>
       <c r="E100">
-        <v>-48.27758525213085</v>
+        <v>-49.00714250666156</v>
       </c>
       <c r="F100">
-        <v>0.1913717752494424</v>
+        <v>-2.092781755108359</v>
       </c>
       <c r="G100">
-        <v>-11.60597838105352</v>
+        <v>-11.9630747208537</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.77566103642641</v>
       </c>
       <c r="E101">
-        <v>-49.79451557774237</v>
+        <v>-50.33962041091479</v>
       </c>
       <c r="F101">
-        <v>-0.7722912187145008</v>
+        <v>-2.034429070152953</v>
       </c>
       <c r="G101">
-        <v>-12.51905105674341</v>
+        <v>-12.07484069679926</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.56956970569008</v>
       </c>
       <c r="E102">
-        <v>-52.14353348586064</v>
+        <v>-52.21791646238549</v>
       </c>
       <c r="F102">
-        <v>-0.6481578783027865</v>
+        <v>-2.356136319806378</v>
       </c>
       <c r="G102">
-        <v>-12.99605106337965</v>
+        <v>-12.57078557156091</v>
       </c>
     </row>
   </sheetData>
